--- a/AAAGameData/DataTables/MapSpawnTable.xlsx
+++ b/AAAGameData/DataTables/MapSpawnTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -62,12 +62,10 @@
     <t>备注</t>
   </si>
   <si>
-    <t>地图ID：
-（对应 SceneTable.Id）</t>
-  </si>
-  <si>
-    <t>生成类型：
-0=敌人 / 1=宝箱</t>
+    <t>地图ID：（对应 SceneTable.Id）</t>
+  </si>
+  <si>
+    <t>生成类型：0=敌人 / 1=宝箱</t>
   </si>
   <si>
     <t>生成目标的配置表ID</t>
@@ -697,13 +695,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1052,322 +1046,238 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="8" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.625" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="32" customWidth="1"/>
+    <col min="5" max="5" width="27" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="40.5" spans="1:8">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:8">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="2">
+      <c r="C5" s="1"/>
+      <c r="D5" s="1">
         <v>2</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>0</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="1">
         <v>1</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="1">
         <v>3</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:8">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="2">
+      <c r="C6" s="1"/>
+      <c r="D6" s="1">
         <v>2</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>0</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="1">
         <v>1</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="1">
         <v>2</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:8">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="2">
+      <c r="C7" s="1"/>
+      <c r="D7" s="1">
         <v>2</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>1</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="1">
         <v>1</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="1">
         <v>1</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <v>50</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:8">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1">
         <v>4</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="2">
+      <c r="C8" s="1"/>
+      <c r="D8" s="1">
         <v>3</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>0</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="1">
         <v>1</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="1">
         <v>2</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:8">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1">
         <v>5</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2">
+      <c r="C9" s="1"/>
+      <c r="D9" s="1">
         <v>3</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>0</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="1">
         <v>1</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="1">
         <v>1</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:8">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1">
         <v>6</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="2">
+      <c r="C10" s="1"/>
+      <c r="D10" s="1">
         <v>3</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>1</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="1">
         <v>1</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="1">
         <v>1</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="C11" s="3"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="C12" s="3"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="C13" s="3"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="C14" s="3"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="C15" s="3"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="C16" s="3"/>
-    </row>
-    <row r="17" spans="3:3">
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18" spans="3:3">
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19" spans="3:3">
-      <c r="C19" s="3"/>
-    </row>
-    <row r="20" spans="3:3">
-      <c r="C20" s="3"/>
-    </row>
-    <row r="21" spans="3:3">
-      <c r="C21" s="3"/>
-    </row>
-    <row r="22" spans="3:3">
-      <c r="C22" s="3"/>
-    </row>
-    <row r="23" spans="3:3">
-      <c r="C23" s="3"/>
-    </row>
-    <row r="24" spans="3:3">
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25" spans="3:3">
-      <c r="C25" s="3"/>
-    </row>
-    <row r="26" spans="3:3">
-      <c r="C26" s="3"/>
-    </row>
-    <row r="27" spans="3:3">
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28" spans="3:3">
-      <c r="C28" s="3"/>
-    </row>
-    <row r="29" spans="3:3">
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="3:3">
-      <c r="C30" s="3"/>
-    </row>
-    <row r="31" spans="3:3">
-      <c r="C31" s="3"/>
-    </row>
-    <row r="32" spans="3:3">
-      <c r="C32" s="3"/>
-    </row>
-    <row r="33" spans="3:3">
-      <c r="C33" s="3"/>
-    </row>
-    <row r="34" spans="3:3">
-      <c r="C34" s="3"/>
-    </row>
-    <row r="35" spans="3:3">
-      <c r="C35" s="3"/>
-    </row>
-    <row r="36" spans="3:3">
-      <c r="C36" s="3"/>
-    </row>
-    <row r="37" spans="3:3">
-      <c r="C37" s="3"/>
-    </row>
-    <row r="38" spans="3:3">
-      <c r="C38" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AAAGameData/DataTables/MapSpawnTable.xlsx
+++ b/AAAGameData/DataTables/MapSpawnTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
   <si>
     <t>#</t>
   </si>
@@ -35,46 +35,70 @@
     <t>MapSpawnTable</t>
   </si>
   <si>
-    <t>Id</t>
-  </si>
-  <si>
     <t>MapId</t>
   </si>
   <si>
-    <t>SpawnType</t>
-  </si>
-  <si>
-    <t>SpawnTargetId</t>
-  </si>
-  <si>
-    <t>Weight</t>
-  </si>
-  <si>
-    <t>ChestLevel</t>
+    <t>SpawnEnemys</t>
+  </si>
+  <si>
+    <t>EnemyNums</t>
+  </si>
+  <si>
+    <t>SpawnTreasures</t>
+  </si>
+  <si>
+    <t>TreasureNums</t>
+  </si>
+  <si>
+    <t>LevelCoefficient</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
-    <t>主键</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>地图ID：（对应 SceneTable.Id）</t>
-  </si>
-  <si>
-    <t>生成类型：0=敌人 / 1=宝箱</t>
-  </si>
-  <si>
-    <t>生成目标的配置表ID</t>
-  </si>
-  <si>
-    <t>权重</t>
-  </si>
-  <si>
-    <t>宝箱等级</t>
+    <t>string</t>
+  </si>
+  <si>
+    <t>int[]</t>
+  </si>
+  <si>
+    <t>地图ID（主键）</t>
+  </si>
+  <si>
+    <t>敌人配置(格式:101:30,102:50)</t>
+  </si>
+  <si>
+    <t>敌人数量范围(min,max)</t>
+  </si>
+  <si>
+    <t>宝箱配置(格式:201:40,202:60)</t>
+  </si>
+  <si>
+    <t>宝箱数量范围(min,max)</t>
+  </si>
+  <si>
+    <t>等级系数范围(min,max)</t>
+  </si>
+  <si>
+    <t>1:30,2:50,3:20</t>
+  </si>
+  <si>
+    <t>10,20</t>
+  </si>
+  <si>
+    <t>1:40,2:60</t>
+  </si>
+  <si>
+    <t>1,10</t>
+  </si>
+  <si>
+    <t>20,30</t>
+  </si>
+  <si>
+    <t>30,40</t>
+  </si>
+  <si>
+    <t>10,30</t>
   </si>
 </sst>
 </file>
@@ -695,9 +719,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1046,20 +1073,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="32" customWidth="1"/>
-    <col min="5" max="5" width="27" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="23" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="7" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1067,216 +1092,120 @@
         <v>1</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="D1" s="2"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="D2" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1" t="s">
-        <v>8</v>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="G4" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:8">
+    <row r="5" ht="15" customHeight="1" spans="1:7">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1">
-        <v>2</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1">
         <v>3</v>
       </c>
-      <c r="H5" s="1">
-        <v>0</v>
+      <c r="C5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:8">
+    <row r="6" ht="15" customHeight="1" spans="1:7">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1">
-        <v>2</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1">
-        <v>2</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" spans="1:8">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1">
-        <v>2</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
-      <c r="H7" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="1:8">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1">
-        <v>3</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1">
-        <v>2</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" spans="1:8">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1">
-        <v>3</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="1:8">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1">
-        <v>6</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1">
-        <v>3</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1</v>
-      </c>
-      <c r="H10" s="1">
-        <v>30</v>
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/MapSpawnTable.xlsx
+++ b/AAAGameData/DataTables/MapSpawnTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
   <si>
     <t>#</t>
   </si>
@@ -65,6 +65,9 @@
     <t>地图ID（主键）</t>
   </si>
   <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>敌人配置(格式:101:30,102:50)</t>
   </si>
   <si>
@@ -78,6 +81,9 @@
   </si>
   <si>
     <t>等级系数范围(min,max)</t>
+  </si>
+  <si>
+    <t>BaseScene</t>
   </si>
   <si>
     <t>1:30,2:50,3:20</t>
@@ -719,9 +725,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1073,140 +1083,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="6"/>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="23" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="7" width="23" customWidth="1"/>
+    <col min="3" max="3" width="8" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="8" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1"/>
+      <c r="C1" s="3"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="1"/>
+      <c r="E1" s="4"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:8">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:8">
+      <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="1:7">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1">
+      <c r="H4" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="1:8">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2">
         <v>3</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>17</v>
+      <c r="C5" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="E5" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="F5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" spans="1:7">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1">
+      <c r="H5" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:8">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2">
         <v>10</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="C6" s="3"/>
       <c r="D6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="G6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="C15" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AAAGameData/DataTables/MapSpawnTable.xlsx
+++ b/AAAGameData/DataTables/MapSpawnTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
   <si>
     <t>#</t>
   </si>
@@ -83,16 +83,19 @@
     <t>等级系数范围(min,max)</t>
   </si>
   <si>
-    <t>BaseScene</t>
+    <t>TutorialScene</t>
   </si>
   <si>
     <t>1:30,2:50,3:20</t>
   </si>
   <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>1:40,2:60</t>
+  </si>
+  <si>
     <t>10,20</t>
-  </si>
-  <si>
-    <t>1:40,2:60</t>
   </si>
   <si>
     <t>1,10</t>
@@ -117,14 +120,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -580,158 +576,158 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1088,7 +1084,7 @@
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="8" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.625" style="1" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
@@ -1201,10 +1197,10 @@
         <v>21</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:8">
@@ -1217,16 +1213,16 @@
         <v>19</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>21</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:8">

--- a/AAAGameData/DataTables/MapSpawnTable.xlsx
+++ b/AAAGameData/DataTables/MapSpawnTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
   <si>
     <t>#</t>
   </si>
@@ -89,13 +89,10 @@
     <t>1:30,2:50,3:20</t>
   </si>
   <si>
-    <t>1,2</t>
+    <t>10,20</t>
   </si>
   <si>
     <t>1:40,2:60</t>
-  </si>
-  <si>
-    <t>10,20</t>
   </si>
   <si>
     <t>1,10</t>
@@ -1080,11 +1077,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="9.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.62962962962963" style="1" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
@@ -1197,10 +1194,10 @@
         <v>21</v>
       </c>
       <c r="G5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:8">
@@ -1213,16 +1210,16 @@
         <v>19</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>21</v>
       </c>
       <c r="G6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:8">

--- a/AAAGameData/DataTables/MapSpawnTable.xlsx
+++ b/AAAGameData/DataTables/MapSpawnTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="15300"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
   <si>
     <t>#</t>
   </si>
@@ -86,16 +86,22 @@
     <t>TutorialScene</t>
   </si>
   <si>
+    <t>1:30,3:20</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>1:40,2:60</t>
+  </si>
+  <si>
+    <t>10,20</t>
+  </si>
+  <si>
+    <t>1,10</t>
+  </si>
+  <si>
     <t>1:30,2:50,3:20</t>
-  </si>
-  <si>
-    <t>10,20</t>
-  </si>
-  <si>
-    <t>1:40,2:60</t>
-  </si>
-  <si>
-    <t>1,10</t>
   </si>
   <si>
     <t>20,30</t>
@@ -1077,11 +1083,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="9.62962962962963" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.63333333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
@@ -1194,10 +1200,10 @@
         <v>21</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:8">
@@ -1207,19 +1213,19 @@
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>21</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:8">

--- a/AAAGameData/DataTables/MapSpawnTable.xlsx
+++ b/AAAGameData/DataTables/MapSpawnTable.xlsx
@@ -89,7 +89,7 @@
     <t>1:30,3:20</t>
   </si>
   <si>
-    <t>1,2</t>
+    <t>1,20</t>
   </si>
   <si>
     <t>1:40,2:60</t>

--- a/AAAGameData/DataTables/MapSpawnTable.xlsx
+++ b/AAAGameData/DataTables/MapSpawnTable.xlsx
@@ -89,7 +89,7 @@
     <t>1:30,3:20</t>
   </si>
   <si>
-    <t>1,20</t>
+    <t>0,0</t>
   </si>
   <si>
     <t>1:40,2:60</t>

--- a/AAAGameData/DataTables/MapSpawnTable.xlsx
+++ b/AAAGameData/DataTables/MapSpawnTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -89,7 +89,7 @@
     <t>1:30,3:20</t>
   </si>
   <si>
-    <t>0,0</t>
+    <t>4,8</t>
   </si>
   <si>
     <t>1:40,2:60</t>
@@ -1083,11 +1083,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="9.63333333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.62962962962963" style="1" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>

--- a/AAAGameData/DataTables/MapSpawnTable.xlsx
+++ b/AAAGameData/DataTables/MapSpawnTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -86,10 +86,10 @@
     <t>TutorialScene</t>
   </si>
   <si>
-    <t>1:30,3:20</t>
-  </si>
-  <si>
-    <t>4,8</t>
+    <t>1:40,3:10</t>
+  </si>
+  <si>
+    <t>2,4</t>
   </si>
   <si>
     <t>1:40,2:60</t>
@@ -1083,11 +1083,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="9.62962962962963" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.63333333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>

--- a/AAAGameData/DataTables/MapSpawnTable.xlsx
+++ b/AAAGameData/DataTables/MapSpawnTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -86,31 +86,31 @@
     <t>TutorialScene</t>
   </si>
   <si>
-    <t>1:40,3:10</t>
-  </si>
-  <si>
-    <t>2,4</t>
-  </si>
-  <si>
-    <t>1:40,2:60</t>
+    <t>1:40,6:20,8:30</t>
+  </si>
+  <si>
+    <t>3,6</t>
+  </si>
+  <si>
+    <t>1:40,2:60,3:30,4:20</t>
   </si>
   <si>
     <t>10,20</t>
   </si>
   <si>
-    <t>1,10</t>
-  </si>
-  <si>
-    <t>1:30,2:50,3:20</t>
-  </si>
-  <si>
-    <t>20,30</t>
-  </si>
-  <si>
-    <t>30,40</t>
-  </si>
-  <si>
-    <t>10,30</t>
+    <t>1,20</t>
+  </si>
+  <si>
+    <t>1:30,3:10,5:10,6:20,7:10,8:20,9:10</t>
+  </si>
+  <si>
+    <t>1:40,2:40,3:30,4:30</t>
+  </si>
+  <si>
+    <t>15,20</t>
+  </si>
+  <si>
+    <t>10,40</t>
   </si>
 </sst>
 </file>
@@ -1083,11 +1083,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="9.63333333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.62962962962963" style="1" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
@@ -1216,10 +1216,10 @@
         <v>24</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>26</v>

--- a/AAAGameData/DataTables/MapSpawnTable.xlsx
+++ b/AAAGameData/DataTables/MapSpawnTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
   <si>
     <t>#</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>1:30,3:10,5:10,6:20,7:10,8:20,9:10</t>
+  </si>
+  <si>
+    <t>15,25</t>
   </si>
   <si>
     <t>1:40,2:40,3:30,4:30</t>
@@ -1083,11 +1086,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="9.62962962962963" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.63333333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
@@ -1216,16 +1219,16 @@
         <v>24</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:8">
